--- a/Apostas_Diarias/Apostas_20260403.xlsx
+++ b/Apostas_Diarias/Apostas_20260403.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/Apostas_Diarias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_2B590F4F9526CA086D439793431510344D07F149" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F71E0794-961E-4682-AEB8-F6BE5CE565BF}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="11_2B590F4F9576402A9DA2DDF0505B283477C7F50E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A60823F7-CC86-4970-9E99-866009E629DF}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="21">
   <si>
     <t>Data</t>
   </si>
@@ -74,16 +74,28 @@
     <t>P1 ⭐</t>
   </si>
   <si>
+    <t>14:30:00</t>
+  </si>
+  <si>
+    <t>ROMANIA 1</t>
+  </si>
+  <si>
+    <t>Botosani x FCSB</t>
+  </si>
+  <si>
+    <t>Lay_CS_0x1_B365</t>
+  </si>
+  <si>
     <t>15:00:00</t>
   </si>
   <si>
-    <t>NETHERLANDS 2</t>
-  </si>
-  <si>
-    <t>MVV Maastricht x RKC Waalwijk</t>
-  </si>
-  <si>
-    <t>Lay_CS_0x1_B365</t>
+    <t>FRANCE 2</t>
+  </si>
+  <si>
+    <t>Annecy x Guingamp</t>
+  </si>
+  <si>
+    <t>Grenoble x Clermont</t>
   </si>
 </sst>
 </file>
@@ -423,14 +435,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="33" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="5" max="5" width="23" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="17" customWidth="1"/>
@@ -494,10 +506,10 @@
         <v>16</v>
       </c>
       <c r="G2">
-        <v>13</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="H2">
-        <v>13</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="I2">
         <v>500</v>
@@ -508,9 +520,89 @@
       </c>
       <c r="K2">
         <f>IF(L2=1,0.935/(H2-1)*I2,-500)</f>
-        <v>38.958333333333336</v>
+        <v>53.125</v>
       </c>
       <c r="L2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3">
+        <v>10.5</v>
+      </c>
+      <c r="H3">
+        <v>10.5</v>
+      </c>
+      <c r="I3">
+        <v>500</v>
+      </c>
+      <c r="J3" t="str">
+        <f t="shared" ref="J3:J4" si="0">IF(L3=1,"GREEN","RED")</f>
+        <v>GREEN</v>
+      </c>
+      <c r="K3">
+        <f t="shared" ref="K3:K4" si="1">IF(L3=1,0.935/(H3-1)*I3,-500)</f>
+        <v>49.210526315789473</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4">
+        <v>10.5</v>
+      </c>
+      <c r="H4">
+        <v>10.5</v>
+      </c>
+      <c r="I4">
+        <v>500</v>
+      </c>
+      <c r="J4" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K4">
+        <f t="shared" si="1"/>
+        <v>49.210526315789473</v>
+      </c>
+      <c r="L4">
         <v>1</v>
       </c>
     </row>

--- a/Apostas_Diarias/Apostas_20260403.xlsx
+++ b/Apostas_Diarias/Apostas_20260403.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/Apostas_Diarias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="11_2B590F4F9576402A9DA2DDF0505B283477C7F50E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A60823F7-CC86-4970-9E99-866009E629DF}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_2B590F4F9526CA086D439793431510344D07F149" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F71E0794-961E-4682-AEB8-F6BE5CE565BF}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Data</t>
   </si>
@@ -74,28 +74,16 @@
     <t>P1 ⭐</t>
   </si>
   <si>
-    <t>14:30:00</t>
-  </si>
-  <si>
-    <t>ROMANIA 1</t>
-  </si>
-  <si>
-    <t>Botosani x FCSB</t>
+    <t>15:00:00</t>
+  </si>
+  <si>
+    <t>NETHERLANDS 2</t>
+  </si>
+  <si>
+    <t>MVV Maastricht x RKC Waalwijk</t>
   </si>
   <si>
     <t>Lay_CS_0x1_B365</t>
-  </si>
-  <si>
-    <t>15:00:00</t>
-  </si>
-  <si>
-    <t>FRANCE 2</t>
-  </si>
-  <si>
-    <t>Annecy x Guingamp</t>
-  </si>
-  <si>
-    <t>Grenoble x Clermont</t>
   </si>
 </sst>
 </file>
@@ -435,14 +423,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="23" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="5" max="5" width="33" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="17" customWidth="1"/>
@@ -506,10 +494,10 @@
         <v>16</v>
       </c>
       <c r="G2">
-        <v>9.8000000000000007</v>
+        <v>13</v>
       </c>
       <c r="H2">
-        <v>9.8000000000000007</v>
+        <v>13</v>
       </c>
       <c r="I2">
         <v>500</v>
@@ -520,89 +508,9 @@
       </c>
       <c r="K2">
         <f>IF(L2=1,0.935/(H2-1)*I2,-500)</f>
-        <v>53.125</v>
+        <v>38.958333333333336</v>
       </c>
       <c r="L2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3">
-        <v>10.5</v>
-      </c>
-      <c r="H3">
-        <v>10.5</v>
-      </c>
-      <c r="I3">
-        <v>500</v>
-      </c>
-      <c r="J3" t="str">
-        <f t="shared" ref="J3:J4" si="0">IF(L3=1,"GREEN","RED")</f>
-        <v>GREEN</v>
-      </c>
-      <c r="K3">
-        <f t="shared" ref="K3:K4" si="1">IF(L3=1,0.935/(H3-1)*I3,-500)</f>
-        <v>49.210526315789473</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4">
-        <v>10.5</v>
-      </c>
-      <c r="H4">
-        <v>10.5</v>
-      </c>
-      <c r="I4">
-        <v>500</v>
-      </c>
-      <c r="J4" t="str">
-        <f t="shared" si="0"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K4">
-        <f t="shared" si="1"/>
-        <v>49.210526315789473</v>
-      </c>
-      <c r="L4">
         <v>1</v>
       </c>
     </row>
